--- a/output/laminas_comunales/comunal_s_fonasa_a_2024_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2024_valparaiso.xlsx
@@ -375,466 +375,466 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5109</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
+          <t>Petorca</t>
         </is>
       </c>
       <c r="C2">
-        <v>268734</v>
+        <v>94.13693729504124</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Juan Fernández</t>
         </is>
       </c>
       <c r="C3">
-        <v>262074</v>
+        <v>93.76391982182628</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5603</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quilpué</t>
+          <t>Cartagena</t>
         </is>
       </c>
       <c r="C4">
-        <v>140202</v>
+        <v>93.19211155094327</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Villa Alemana</t>
+          <t>Isla de Pascua</t>
         </is>
       </c>
       <c r="C5">
-        <v>115172</v>
+        <v>92.54256526674234</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Santa María</t>
         </is>
       </c>
       <c r="C6">
-        <v>94020</v>
+        <v>92.46935201401051</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Putaendo</t>
         </is>
       </c>
       <c r="C7">
-        <v>88628</v>
+        <v>92.46173201929126</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Catemu</t>
         </is>
       </c>
       <c r="C8">
-        <v>72208</v>
+        <v>92.4506683640993</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="C9">
-        <v>58394</v>
+        <v>91.11083116102836</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Limache</t>
+          <t>La Ligua</t>
         </is>
       </c>
       <c r="C10">
-        <v>49871</v>
+        <v>90.7891609222724</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>La Ligua</t>
+          <t>Cabildo</t>
         </is>
       </c>
       <c r="C11">
-        <v>38195</v>
+        <v>90.76721883173497</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Concón</t>
+          <t>Hijuelas</t>
         </is>
       </c>
       <c r="C12">
-        <v>36305</v>
+        <v>90.69383013894473</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Quintero</t>
+          <t>Panquehue</t>
         </is>
       </c>
       <c r="C13">
-        <v>32846</v>
+        <v>90.54863554245507</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>El Tabo</t>
         </is>
       </c>
       <c r="C14">
-        <v>29439</v>
+        <v>88.4821099225378</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cartagena</t>
+          <t>Nogales</t>
         </is>
       </c>
       <c r="C15">
-        <v>26132</v>
+        <v>88.46105919003115</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Calera</t>
+          <t>El Quisco</t>
         </is>
       </c>
       <c r="C16">
-        <v>25078</v>
+        <v>88.45766790636623</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Puchuncaví</t>
+          <t>Llaillay</t>
         </is>
       </c>
       <c r="C17">
-        <v>23098</v>
+        <v>88.31959010487552</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nogales</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="C18">
-        <v>21297</v>
+        <v>88.04350476747872</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>La Cruz</t>
+          <t>Calle Larga</t>
         </is>
       </c>
       <c r="C19">
-        <v>21254</v>
+        <v>87.47417507821262</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cabildo</t>
+          <t>Casablanca</t>
         </is>
       </c>
       <c r="C20">
-        <v>20822</v>
+        <v>87.4728866438865</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
+          <t>Limache</t>
         </is>
       </c>
       <c r="C21">
-        <v>20300</v>
+        <v>86.98632526337822</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>El Quisco</t>
+          <t>Quintero</t>
         </is>
       </c>
       <c r="C22">
-        <v>20217</v>
+        <v>86.85741485085678</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>El Tabo</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="C23">
-        <v>19190</v>
+        <v>86.48574802150726</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Olmué</t>
+          <t>Calera</t>
         </is>
       </c>
       <c r="C24">
-        <v>18718</v>
+        <v>86.33891069338291</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>San Esteban</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="C25">
-        <v>18242</v>
+        <v>86.32583081620754</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5705</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Putaendo</t>
+          <t>Puchuncaví</t>
         </is>
       </c>
       <c r="C26">
-        <v>17638</v>
+        <v>86.22839437040355</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
+          <t>Olmué</t>
         </is>
       </c>
       <c r="C27">
-        <v>17366</v>
+        <v>86.18260509231548</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Santa María</t>
+          <t>San Esteban</t>
         </is>
       </c>
       <c r="C28">
-        <v>15312</v>
+        <v>85.25494228162826</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Calle Larga</t>
+          <t>Papudo</t>
         </is>
       </c>
       <c r="C29">
-        <v>14819</v>
+        <v>85.19455487290688</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Catemu</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="C30">
-        <v>14524</v>
+        <v>83.70219597500143</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
+          <t>Villa Alemana</t>
         </is>
       </c>
       <c r="C31">
-        <v>12595</v>
+        <v>83.48458928933863</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Llaillay</t>
+          <t>Quilpué</t>
         </is>
       </c>
       <c r="C32">
-        <v>11032</v>
+        <v>82.53245033112583</v>
       </c>
     </row>
     <row r="33">
@@ -849,37 +849,37 @@
         </is>
       </c>
       <c r="C33">
-        <v>10616</v>
+        <v>81.91358024691358</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Panquehue</t>
+          <t>Algarrobo</t>
         </is>
       </c>
       <c r="C34">
-        <v>9523</v>
+        <v>79.7776552737964</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Petorca</t>
+          <t>La Cruz</t>
         </is>
       </c>
       <c r="C35">
-        <v>9473</v>
+        <v>78.76227533815083</v>
       </c>
     </row>
     <row r="36">
@@ -894,52 +894,52 @@
         </is>
       </c>
       <c r="C36">
-        <v>8833</v>
+        <v>77.96804660605525</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Isla de Pascua</t>
+          <t>Viña del Mar</t>
         </is>
       </c>
       <c r="C37">
-        <v>8153</v>
+        <v>77.84743023006553</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Papudo</t>
+          <t>Santo Domingo</t>
         </is>
       </c>
       <c r="C38">
-        <v>7072</v>
+        <v>75.28842130432183</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Juan Fernández</t>
+          <t>Concón</t>
         </is>
       </c>
       <c r="C39">
-        <v>842</v>
+        <v>65.40734335026843</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +995,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
